--- a/data/pairing/a_valider_2023.xlsx
+++ b/data/pairing/a_valider_2023.xlsx
@@ -1560,12 +1560,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Stock des PME | 2018 = 255 059 millions de Francs CFA
-Stock des PME | 2019 (e) = 287 376 millions de Francs CFA
-Stock des PME | 2020 (e) = 288 850 millions de Francs CFA
-Stock des PME | 2021 (e) = 324 250 millions de Francs CFA
-Stock des PME | 2022 (e) = 349 722 millions de Francs CFA
-Stock des PME | 2023 (e) = 393 166 millions de Francs CFA
+          <t>Stock des PME | 2018 = 255 059
+Stock des PME | 2019 (e) = 287 376
+Stock des PME | 2020 (e) = 288 850
+Stock des PME | 2021 (e) = 324 250
+Stock des PME | 2022 (e) = 349 722
+Stock des PME | 2023 (e) = 393 166
 VA des PME | 2018 = 4 359 millions de Francs CFA
 VA des PME | 2019 (e) = 4 911 millions de Francs CFA
 VA des PME | 2020 (e) = 4 936 millions de Francs CFA
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Stock des PME | 2018 = 255 059 millions de Francs CFA
-Stock des PME | 2019 (e) = 287 376 millions de Francs CFA
-Stock des PME | 2020 (e) = 288 850 millions de Francs CFA
-Stock des PME | 2021 (e) = 324 250 millions de Francs CFA
-Stock des PME | 2022 (e) = 349 722 millions de Francs CFA
-Stock des PME | 2023 (e) = 393 166 millions de Francs CFA
+          <t>Stock des PME | 2018 = 255 059
+Stock des PME | 2019 (e) = 287 376
+Stock des PME | 2020 (e) = 288 850
+Stock des PME | 2021 (e) = 324 250
+Stock des PME | 2022 (e) = 349 722
+Stock des PME | 2023 (e) = 393 166
 VA des PME | 2018 = 4 359 millions de Francs CFA
 VA des PME | 2019 (e) = 4 911 millions de Francs CFA
 VA des PME | 2020 (e) = 4 936 millions de Francs CFA
